--- a/templates/test-data/Outreach Test Data.xlsx
+++ b/templates/test-data/Outreach Test Data.xlsx
@@ -503,7 +503,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46050.45416666667</v>
+        <v>46050.45555555556</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>46050.45833333334</v>
@@ -540,7 +540,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46050.60208333333</v>
+        <v>46050.59930555556</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>46050.60416666666</v>
@@ -577,7 +577,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46067.50555555556</v>
+        <v>46067.50625</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>46067.51041666666</v>
@@ -614,7 +614,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46074.53819444445</v>
+        <v>46074.53888888889</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>46074.54166666666</v>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46089.47638888889</v>
+        <v>46089.47361111111</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>46089.47916666666</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46089.56805555556</v>
+        <v>46089.56736111111</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>46089.57291666666</v>
@@ -725,7 +725,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46102.57916666667</v>
+        <v>46102.58125</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46102.58333333334</v>
@@ -762,7 +762,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46122.51805555556</v>
+        <v>46122.51597222222</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>46122.52083333334</v>
@@ -799,7 +799,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46124.54652777778</v>
+        <v>46124.54861111111</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>46124.55208333334</v>
@@ -836,7 +836,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46130.45277777778</v>
+        <v>46130.45625</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46130.45833333334</v>
@@ -873,7 +873,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46136.49791666667</v>
+        <v>46136.49513888889</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46136.5</v>
